--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2B863C1-9A5D-4BE6-B5CB-1AC593988C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055C2F9E-73BA-4DA9-A3AC-988E2663BC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12683" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4290" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="1122">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -3490,6 +3490,9 @@
   </si>
   <si>
     <t>e_w116541259-400_IND</t>
+  </si>
+  <si>
+    <t>START</t>
   </si>
 </sst>
 </file>
@@ -20684,8 +20687,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE88C03C-7FBC-4235-80D9-1369C1D26EC7}">
-  <dimension ref="B9:S128"/>
+  <dimension ref="B9:S130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="21.265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="2:19">
       <c r="B9" t="s">
@@ -24177,6 +24183,28 @@
       </c>
       <c r="K128" t="s">
         <v>1095</v>
+      </c>
+    </row>
+    <row r="129" spans="2:11">
+      <c r="B129" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E129">
+        <v>2100</v>
+      </c>
+      <c r="K129" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="130" spans="2:11">
+      <c r="B130" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E130">
+        <v>2100</v>
+      </c>
+      <c r="K130" t="s">
+        <v>1121</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055C2F9E-73BA-4DA9-A3AC-988E2663BC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE9958B-8AD6-4C5C-9C42-781C8571A6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="1121">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -3481,9 +3481,6 @@
   </si>
   <si>
     <t>en_geothermal</t>
-  </si>
-  <si>
-    <t>yes</t>
   </si>
   <si>
     <t>CHP</t>
@@ -5426,7 +5423,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -20792,7 +20789,7 @@
         <v>418</v>
       </c>
       <c r="S11" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="2:19">
@@ -20833,7 +20830,7 @@
         <v>418</v>
       </c>
       <c r="S12" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="2:19">
@@ -20859,7 +20856,7 @@
         <v>1093</v>
       </c>
       <c r="M13" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N13" t="s">
         <v>1097</v>
@@ -20874,7 +20871,7 @@
         <v>418</v>
       </c>
       <c r="S13" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="2:19">
@@ -20915,7 +20912,7 @@
         <v>418</v>
       </c>
       <c r="S14" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="2:19">
@@ -20965,7 +20962,7 @@
         <v>418</v>
       </c>
       <c r="S15" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="2:19">
@@ -21015,7 +21012,7 @@
         <v>418</v>
       </c>
       <c r="S16" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="2:19">
@@ -21056,7 +21053,7 @@
         <v>418</v>
       </c>
       <c r="S17" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="2:19">
@@ -21097,7 +21094,7 @@
         <v>418</v>
       </c>
       <c r="S18" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="2:19">
@@ -21138,7 +21135,7 @@
         <v>418</v>
       </c>
       <c r="S19" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="2:19">
@@ -21179,7 +21176,7 @@
         <v>418</v>
       </c>
       <c r="S20" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="2:19">
@@ -21229,7 +21226,7 @@
         <v>418</v>
       </c>
       <c r="S21" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="2:19">
@@ -21279,7 +21276,7 @@
         <v>418</v>
       </c>
       <c r="S22" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="2:19">
@@ -21320,7 +21317,7 @@
         <v>418</v>
       </c>
       <c r="S23" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="2:19">
@@ -21361,7 +21358,7 @@
         <v>418</v>
       </c>
       <c r="S24" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="2:19">
@@ -21402,7 +21399,7 @@
         <v>418</v>
       </c>
       <c r="S25" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="2:19">
@@ -21443,7 +21440,7 @@
         <v>418</v>
       </c>
       <c r="S26" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="2:19">
@@ -21478,7 +21475,7 @@
         <v>1094</v>
       </c>
       <c r="M27" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N27" t="s">
         <v>1115</v>
@@ -21493,7 +21490,7 @@
         <v>418</v>
       </c>
       <c r="S27" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:19">
@@ -21543,7 +21540,7 @@
         <v>418</v>
       </c>
       <c r="S28" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="2:19">
@@ -21593,7 +21590,7 @@
         <v>418</v>
       </c>
       <c r="S29" t="s">
-        <v>1118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="2:19">
@@ -24193,7 +24190,7 @@
         <v>2100</v>
       </c>
       <c r="K129" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -24204,7 +24201,7 @@
         <v>2100</v>
       </c>
       <c r="K130" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
